--- a/2026/GAEBELER 1949/Febrero/Febrero Gaebeler.xlsx
+++ b/2026/GAEBELER 1949/Febrero/Febrero Gaebeler.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\GAEBELER 1949\Febrero\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\GAEBELER 1949\Febrero\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABD439D-227C-45B3-BA1A-6DC9A94A6121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{218D85FA-5E3D-4645-97F9-43529032F0FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,16 @@
     <sheet name="Edesur" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$M$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">Edesur!$A$1:$M$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$O$26</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$85</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1405,6 +1410,10 @@
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="170" fontId="27" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="9" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1435,6 +1444,24 @@
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1447,9 +1474,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1459,28 +1483,13 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="11" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1497,10 +1506,6 @@
     <xf numFmtId="169" fontId="25" fillId="0" borderId="39" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="18" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="10" fillId="8" borderId="13" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="9" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Millares 2" xfId="4" xr:uid="{769376F3-FA42-4CBE-8FC6-971888C358BE}"/>
@@ -1581,9 +1586,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1621,9 +1626,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1656,9 +1661,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1691,9 +1713,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1868,20 +1907,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M89"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="15"/>
       <c r="B1" s="60" t="s">
         <v>68</v>
@@ -1890,16 +1929,16 @@
       <c r="D1" s="60"/>
       <c r="E1" s="61"/>
     </row>
-    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="16"/>
-      <c r="B2" s="188" t="s">
+      <c r="B2" s="192" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="188"/>
-      <c r="D2" s="188"/>
-      <c r="E2" s="189"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C2" s="192"/>
+      <c r="D2" s="192"/>
+      <c r="E2" s="193"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="16"/>
       <c r="B3" s="179" t="s">
         <v>25</v>
@@ -1908,7 +1947,7 @@
       <c r="D3" s="17"/>
       <c r="E3" s="18"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="16"/>
       <c r="B4" s="17" t="s">
         <v>84</v>
@@ -1917,7 +1956,7 @@
       <c r="D4" s="17"/>
       <c r="E4" s="18"/>
     </row>
-    <row r="5" spans="1:5" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="180" t="s">
         <v>83</v>
       </c>
@@ -1928,56 +1967,56 @@
       </c>
       <c r="E5" s="182"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="195" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="199" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="195"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="195"/>
-      <c r="C8" s="195"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="195"/>
-      <c r="C9" s="195"/>
-    </row>
-    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="194" t="s">
+      <c r="C7" s="199"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="199"/>
+      <c r="C8" s="199"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="199"/>
+      <c r="C9" s="199"/>
+    </row>
+    <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="198" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="194"/>
-      <c r="C12" s="194"/>
-      <c r="D12" s="194"/>
-      <c r="E12" s="194"/>
-    </row>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="194"/>
-      <c r="B13" s="194"/>
-      <c r="C13" s="194"/>
-      <c r="D13" s="194"/>
-      <c r="E13" s="194"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="194"/>
-      <c r="B14" s="194"/>
-      <c r="C14" s="194"/>
-      <c r="D14" s="194"/>
-      <c r="E14" s="194"/>
-    </row>
-    <row r="15" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="194"/>
-      <c r="B15" s="194"/>
-      <c r="C15" s="194"/>
-      <c r="D15" s="194"/>
-      <c r="E15" s="194"/>
-    </row>
-    <row r="16" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="198"/>
+      <c r="C12" s="198"/>
+      <c r="D12" s="198"/>
+      <c r="E12" s="198"/>
+    </row>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="198"/>
+      <c r="B13" s="198"/>
+      <c r="C13" s="198"/>
+      <c r="D13" s="198"/>
+      <c r="E13" s="198"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="198"/>
+      <c r="B14" s="198"/>
+      <c r="C14" s="198"/>
+      <c r="D14" s="198"/>
+      <c r="E14" s="198"/>
+    </row>
+    <row r="15" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="198"/>
+      <c r="B15" s="198"/>
+      <c r="C15" s="198"/>
+      <c r="D15" s="198"/>
+      <c r="E15" s="198"/>
+    </row>
+    <row r="16" spans="1:5" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="17" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>5</v>
       </c>
@@ -1986,7 +2025,7 @@
       <c r="D19" s="9"/>
       <c r="E19" s="14"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="31" t="s">
         <v>81</v>
       </c>
@@ -1995,29 +2034,29 @@
       <c r="D20" s="114"/>
       <c r="E20" s="115"/>
     </row>
-    <row r="21" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="186" t="s">
+    <row r="21" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="190" t="s">
         <v>89</v>
       </c>
-      <c r="B21" s="187"/>
+      <c r="B21" s="191"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="218">
+      <c r="D21" s="186">
         <v>52745</v>
       </c>
       <c r="E21" s="117"/>
     </row>
-    <row r="22" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="186" t="s">
+    <row r="22" spans="1:7" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="190" t="s">
         <v>90</v>
       </c>
-      <c r="B22" s="187"/>
+      <c r="B22" s="191"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="218">
+      <c r="D22" s="186">
         <v>52745</v>
       </c>
       <c r="E22" s="117"/>
     </row>
-    <row r="23" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="26" t="s">
         <v>82</v>
       </c>
@@ -2029,7 +2068,7 @@
         <v>105490</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
         <v>4</v>
       </c>
@@ -2041,31 +2080,31 @@
         <v>105490</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="5"/>
       <c r="B25" s="5"/>
       <c r="C25" s="5"/>
       <c r="D25" s="78"/>
       <c r="E25" s="84"/>
     </row>
-    <row r="26" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="27" t="s">
         <v>95</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
       <c r="D26" s="85"/>
-      <c r="E26" s="220">
+      <c r="E26" s="188">
         <v>1000000</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
       <c r="D27" s="86"/>
       <c r="E27" s="87"/>
       <c r="F27" s="39"/>
     </row>
-    <row r="28" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>7</v>
       </c>
@@ -2079,15 +2118,15 @@
       <c r="F28" s="111"/>
       <c r="G28" s="39"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D29" s="86"/>
       <c r="E29" s="86"/>
     </row>
-    <row r="30" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D30" s="86"/>
       <c r="E30" s="86"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>30</v>
       </c>
@@ -2096,35 +2135,35 @@
       <c r="D31" s="90"/>
       <c r="E31" s="91"/>
     </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="186"/>
-      <c r="B32" s="187"/>
+    <row r="32" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="190"/>
+      <c r="B32" s="191"/>
       <c r="C32" s="5"/>
       <c r="D32" s="100"/>
       <c r="E32" s="79"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="186"/>
-      <c r="B33" s="187"/>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="190"/>
+      <c r="B33" s="191"/>
       <c r="C33" s="5"/>
       <c r="D33" s="81"/>
       <c r="E33" s="79"/>
     </row>
-    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="192"/>
-      <c r="B34" s="193"/>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="196"/>
+      <c r="B34" s="197"/>
       <c r="C34" s="5"/>
       <c r="D34" s="81"/>
       <c r="E34" s="79"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="80"/>
       <c r="B35" s="82"/>
       <c r="C35" s="5"/>
       <c r="D35" s="81"/>
       <c r="E35" s="79"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="45"/>
       <c r="B36" s="44"/>
       <c r="C36" s="44"/>
@@ -2134,9 +2173,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="39" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="27" t="s">
         <v>10</v>
       </c>
@@ -2145,8 +2184,8 @@
       <c r="D39" s="28"/>
       <c r="E39" s="77"/>
     </row>
-    <row r="40" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="41" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>11</v>
       </c>
@@ -2158,8 +2197,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="75" t="s">
         <v>8</v>
       </c>
@@ -2168,7 +2207,7 @@
         <v>1105490</v>
       </c>
     </row>
-    <row r="44" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="75" t="s">
         <v>9</v>
       </c>
@@ -2177,7 +2216,7 @@
         <v>105490</v>
       </c>
     </row>
-    <row r="45" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="75" t="s">
         <v>12</v>
       </c>
@@ -2186,7 +2225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="75" t="s">
         <v>26</v>
       </c>
@@ -2195,44 +2234,44 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="190"/>
-      <c r="B49" s="190"/>
-      <c r="C49" s="190"/>
-      <c r="D49" s="190"/>
-      <c r="E49" s="190"/>
-    </row>
-    <row r="50" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="190"/>
-      <c r="B50" s="190"/>
-      <c r="C50" s="190"/>
-      <c r="D50" s="190"/>
-      <c r="E50" s="190"/>
-    </row>
-    <row r="51" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="190"/>
-      <c r="B51" s="190"/>
-      <c r="C51" s="190"/>
-      <c r="D51" s="190"/>
-      <c r="E51" s="190"/>
-    </row>
-    <row r="53" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" ht="73.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" spans="1:5" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="194"/>
+      <c r="B49" s="194"/>
+      <c r="C49" s="194"/>
+      <c r="D49" s="194"/>
+      <c r="E49" s="194"/>
+    </row>
+    <row r="50" spans="1:6" ht="106.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="194"/>
+      <c r="B50" s="194"/>
+      <c r="C50" s="194"/>
+      <c r="D50" s="194"/>
+      <c r="E50" s="194"/>
+    </row>
+    <row r="51" spans="1:6" ht="15.75" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="194"/>
+      <c r="B51" s="194"/>
+      <c r="C51" s="194"/>
+      <c r="D51" s="194"/>
+      <c r="E51" s="194"/>
+    </row>
+    <row r="53" spans="1:6" ht="0.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="20" t="s">
         <v>22</v>
       </c>
       <c r="B53" s="97"/>
       <c r="C53" s="21"/>
     </row>
-    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="30"/>
       <c r="B54" s="52">
         <v>0</v>
       </c>
       <c r="C54" s="23"/>
     </row>
-    <row r="55" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="22" t="s">
         <v>2</v>
       </c>
@@ -2242,14 +2281,14 @@
       </c>
       <c r="C55" s="21"/>
     </row>
-    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="22"/>
       <c r="B56" s="36">
         <v>0</v>
       </c>
       <c r="C56" s="21"/>
     </row>
-    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="22" t="s">
         <v>27</v>
       </c>
@@ -2259,19 +2298,19 @@
       </c>
       <c r="C57" s="21"/>
     </row>
-    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="25"/>
       <c r="B58" s="43"/>
       <c r="C58" s="21"/>
     </row>
-    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="96" t="s">
         <v>31</v>
       </c>
       <c r="B59" s="43"/>
       <c r="C59" s="21"/>
     </row>
-    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="35" t="s">
         <v>13</v>
       </c>
@@ -2281,7 +2320,7 @@
       </c>
       <c r="C60" s="21"/>
     </row>
-    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="25" t="s">
         <v>14</v>
       </c>
@@ -2291,7 +2330,7 @@
       </c>
       <c r="C61" s="21"/>
     </row>
-    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="29" t="s">
         <v>4</v>
       </c>
@@ -2302,33 +2341,33 @@
       <c r="C62" s="24"/>
       <c r="D62" s="39"/>
     </row>
-    <row r="63" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" ht="34.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="37"/>
       <c r="C63" s="24"/>
       <c r="D63" s="39"/>
       <c r="E63" s="98"/>
       <c r="F63" s="99"/>
     </row>
-    <row r="64" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="38"/>
       <c r="C64" s="24"/>
     </row>
-    <row r="65" spans="1:4" s="34" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" s="34" customFormat="1" ht="27" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65"/>
       <c r="B65" s="37"/>
       <c r="C65" s="33"/>
     </row>
-    <row r="66" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" s="34" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A66" s="102" t="s">
         <v>96</v>
       </c>
-      <c r="B66" s="221">
+      <c r="B66" s="189">
         <v>-345093.76999999996</v>
       </c>
       <c r="C66" s="33"/>
       <c r="D66" s="42"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="48" t="s">
         <v>34</v>
       </c>
@@ -2337,7 +2376,7 @@
         <v>-105490</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A68" s="48" t="s">
         <v>35</v>
       </c>
@@ -2346,7 +2385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A69" s="48" t="s">
         <v>39</v>
       </c>
@@ -2355,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="48" t="s">
         <v>91</v>
       </c>
@@ -2364,7 +2403,7 @@
         <v>-310242.59999999998</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="48" t="s">
         <v>91</v>
       </c>
@@ -2373,7 +2412,7 @@
         <v>-544144.18999999994</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="48" t="s">
         <v>91</v>
       </c>
@@ -2382,7 +2421,7 @@
         <v>-555834.79</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="48" t="s">
         <v>91</v>
       </c>
@@ -2390,7 +2429,7 @@
         <v>-452185.43</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="48" t="s">
         <v>91</v>
       </c>
@@ -2399,7 +2438,7 @@
       </c>
       <c r="D74" s="39"/>
     </row>
-    <row r="75" spans="1:4" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="48" t="s">
         <v>36</v>
       </c>
@@ -2408,13 +2447,13 @@
         <v>236613.83</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="109" t="s">
         <v>37</v>
       </c>
       <c r="B76" s="110"/>
     </row>
-    <row r="77" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A77" s="105" t="s">
         <v>32</v>
       </c>
@@ -2423,24 +2462,24 @@
         <v>-2735183.96</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="103"/>
       <c r="B78" s="103"/>
     </row>
-    <row r="79" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A80" s="191" t="s">
+    <row r="79" spans="1:4" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="195" t="s">
         <v>21</v>
       </c>
-      <c r="B80" s="191"/>
-      <c r="C80" s="191"/>
-    </row>
-    <row r="81" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A81" s="191"/>
-      <c r="B81" s="191"/>
-      <c r="C81" s="191"/>
-    </row>
-    <row r="82" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="195"/>
+      <c r="C80" s="195"/>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" s="195"/>
+      <c r="B81" s="195"/>
+      <c r="C81" s="195"/>
+    </row>
+    <row r="82" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="93"/>
       <c r="B82" s="32"/>
       <c r="C82" s="32">
@@ -2448,13 +2487,13 @@
       </c>
       <c r="E82" s="111"/>
     </row>
-    <row r="83" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="93"/>
       <c r="B83" s="95"/>
       <c r="C83" s="92"/>
       <c r="D83" s="111"/>
     </row>
-    <row r="84" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="40" t="s">
         <v>4</v>
       </c>
@@ -2464,36 +2503,36 @@
       </c>
       <c r="C84" s="41"/>
     </row>
-    <row r="85" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M85" s="8"/>
     </row>
-    <row r="86" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="190"/>
-      <c r="B86" s="190"/>
-      <c r="C86" s="190"/>
-      <c r="D86" s="190"/>
-      <c r="E86" s="190"/>
-    </row>
-    <row r="87" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A87" s="190"/>
-      <c r="B87" s="190"/>
-      <c r="C87" s="190"/>
-      <c r="D87" s="190"/>
-      <c r="E87" s="190"/>
-    </row>
-    <row r="88" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A88" s="190"/>
-      <c r="B88" s="190"/>
-      <c r="C88" s="190"/>
-      <c r="D88" s="190"/>
-      <c r="E88" s="190"/>
-    </row>
-    <row r="89" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A89" s="190"/>
-      <c r="B89" s="190"/>
-      <c r="C89" s="190"/>
-      <c r="D89" s="190"/>
-      <c r="E89" s="190"/>
+    <row r="86" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="194"/>
+      <c r="B86" s="194"/>
+      <c r="C86" s="194"/>
+      <c r="D86" s="194"/>
+      <c r="E86" s="194"/>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" s="194"/>
+      <c r="B87" s="194"/>
+      <c r="C87" s="194"/>
+      <c r="D87" s="194"/>
+      <c r="E87" s="194"/>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" s="194"/>
+      <c r="B88" s="194"/>
+      <c r="C88" s="194"/>
+      <c r="D88" s="194"/>
+      <c r="E88" s="194"/>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" s="194"/>
+      <c r="B89" s="194"/>
+      <c r="C89" s="194"/>
+      <c r="D89" s="194"/>
+      <c r="E89" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -2518,29 +2557,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.5546875" customWidth="1"/>
-    <col min="3" max="3" width="0.109375" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" customWidth="1"/>
-    <col min="6" max="6" width="12.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.6640625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" customWidth="1"/>
-    <col min="10" max="10" width="0.109375" customWidth="1"/>
-    <col min="11" max="11" width="12.44140625" customWidth="1"/>
-    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.6640625" customWidth="1"/>
-    <col min="14" max="14" width="0.44140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="14.33203125" customWidth="1"/>
-    <col min="16" max="16" width="7.109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="2" width="18.5703125" customWidth="1"/>
+    <col min="3" max="3" width="0.140625" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.28515625" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="9" max="9" width="9.5703125" customWidth="1"/>
+    <col min="10" max="10" width="0.140625" customWidth="1"/>
+    <col min="11" max="11" width="12.42578125" customWidth="1"/>
+    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" customWidth="1"/>
+    <col min="14" max="14" width="0.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="12" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="17" t="str">
         <f>RESUMEN!B4</f>
@@ -2560,17 +2599,17 @@
       <c r="N1" s="6"/>
       <c r="O1" s="6"/>
     </row>
-    <row r="2" spans="1:18" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
-      <c r="B2" s="196" t="s">
+      <c r="B2" s="206" t="s">
         <v>86</v>
       </c>
-      <c r="C2" s="196"/>
-      <c r="D2" s="196"/>
-      <c r="E2" s="196"/>
-      <c r="F2" s="196"/>
-      <c r="G2" s="196"/>
-      <c r="H2" s="196"/>
+      <c r="C2" s="206"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="206"/>
+      <c r="F2" s="206"/>
+      <c r="G2" s="206"/>
+      <c r="H2" s="206"/>
       <c r="I2" s="6"/>
       <c r="J2" s="7"/>
       <c r="K2" s="6" t="s">
@@ -2584,15 +2623,15 @@
       <c r="O2" s="49"/>
       <c r="P2" s="19"/>
     </row>
-    <row r="3" spans="1:18" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
-      <c r="B3" s="197"/>
-      <c r="C3" s="197"/>
-      <c r="D3" s="197"/>
-      <c r="E3" s="197"/>
-      <c r="F3" s="197"/>
-      <c r="G3" s="197"/>
-      <c r="H3" s="197"/>
+      <c r="B3" s="207"/>
+      <c r="C3" s="207"/>
+      <c r="D3" s="207"/>
+      <c r="E3" s="207"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="207"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
       <c r="K3" s="6"/>
@@ -2601,7 +2640,7 @@
       <c r="N3" s="50"/>
       <c r="O3" s="53"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" s="200" t="s">
         <v>0</v>
       </c>
@@ -2614,7 +2653,7 @@
       <c r="D4" s="200" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="204" t="s">
+      <c r="E4" s="202" t="s">
         <v>33</v>
       </c>
       <c r="F4" s="200" t="s">
@@ -2623,53 +2662,53 @@
       <c r="G4" s="200" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="210" t="s">
+      <c r="H4" s="204" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="204" t="s">
+      <c r="I4" s="202" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="204" t="s">
+      <c r="J4" s="202" t="s">
         <v>3</v>
       </c>
-      <c r="K4" s="204" t="s">
+      <c r="K4" s="202" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="207" t="s">
+      <c r="L4" s="214" t="s">
         <v>91</v>
       </c>
       <c r="M4" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="N4" s="202" t="s">
+      <c r="N4" s="211" t="s">
         <v>15</v>
       </c>
-      <c r="O4" s="198" t="s">
+      <c r="O4" s="208" t="s">
         <v>23</v>
       </c>
       <c r="R4" s="39"/>
     </row>
-    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="209"/>
-      <c r="B5" s="209"/>
-      <c r="C5" s="201"/>
-      <c r="D5" s="209"/>
-      <c r="E5" s="206"/>
-      <c r="F5" s="209"/>
-      <c r="G5" s="201"/>
-      <c r="H5" s="211"/>
-      <c r="I5" s="206"/>
-      <c r="J5" s="205"/>
-      <c r="K5" s="206"/>
-      <c r="L5" s="208"/>
+    <row r="5" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="201"/>
+      <c r="B5" s="201"/>
+      <c r="C5" s="210"/>
+      <c r="D5" s="201"/>
+      <c r="E5" s="203"/>
+      <c r="F5" s="201"/>
+      <c r="G5" s="210"/>
+      <c r="H5" s="205"/>
+      <c r="I5" s="203"/>
+      <c r="J5" s="213"/>
+      <c r="K5" s="203"/>
+      <c r="L5" s="215"/>
       <c r="M5" s="54" t="str">
         <f>RESUMEN!B7</f>
         <v>VTO 20/03</v>
       </c>
-      <c r="N5" s="203"/>
-      <c r="O5" s="199"/>
-    </row>
-    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N5" s="212"/>
+      <c r="O5" s="209"/>
+    </row>
+    <row r="6" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="57" t="s">
         <v>44</v>
       </c>
@@ -2684,7 +2723,7 @@
       <c r="E6" s="63">
         <v>32089.01</v>
       </c>
-      <c r="F6" s="219">
+      <c r="F6" s="187">
         <f>E6</f>
         <v>32089.01</v>
       </c>
@@ -2724,7 +2763,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="57" t="s">
         <v>45</v>
       </c>
@@ -2739,7 +2778,7 @@
       <c r="E7" s="63">
         <v>20456.02</v>
       </c>
-      <c r="F7" s="219">
+      <c r="F7" s="187">
         <f>E7</f>
         <v>20456.02</v>
       </c>
@@ -2783,7 +2822,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="57" t="s">
         <v>47</v>
       </c>
@@ -2798,7 +2837,7 @@
       <c r="E8" s="63">
         <v>15028.03</v>
       </c>
-      <c r="F8" s="219">
+      <c r="F8" s="187">
         <f>E8</f>
         <v>15028.03</v>
       </c>
@@ -2839,7 +2878,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="57" t="s">
         <v>48</v>
       </c>
@@ -2893,7 +2932,7 @@
       </c>
       <c r="R9" s="39"/>
     </row>
-    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="57" t="s">
         <v>49</v>
       </c>
@@ -2947,7 +2986,7 @@
       </c>
       <c r="R10" s="39"/>
     </row>
-    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="57" t="s">
         <v>50</v>
       </c>
@@ -2962,7 +3001,7 @@
       <c r="E11" s="63">
         <v>14590.06</v>
       </c>
-      <c r="F11" s="219">
+      <c r="F11" s="187">
         <v>15028.06</v>
       </c>
       <c r="G11" s="64"/>
@@ -3005,7 +3044,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="57" t="s">
         <v>51</v>
       </c>
@@ -3058,7 +3097,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="57" t="s">
         <v>53</v>
       </c>
@@ -3073,7 +3112,7 @@
       <c r="E13" s="63">
         <v>21070.080000000002</v>
       </c>
-      <c r="F13" s="219">
+      <c r="F13" s="187">
         <v>20456.080000000002</v>
       </c>
       <c r="G13" s="64"/>
@@ -3113,7 +3152,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="57" t="s">
         <v>54</v>
       </c>
@@ -3128,7 +3167,7 @@
       <c r="E14" s="63">
         <v>14590.09</v>
       </c>
-      <c r="F14" s="219">
+      <c r="F14" s="187">
         <v>15028.09</v>
       </c>
       <c r="G14" s="64"/>
@@ -3171,7 +3210,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="57" t="s">
         <v>55</v>
       </c>
@@ -3186,7 +3225,7 @@
       <c r="E15" s="63">
         <v>32089.1</v>
       </c>
-      <c r="F15" s="219">
+      <c r="F15" s="187">
         <f>E15</f>
         <v>32089.1</v>
       </c>
@@ -3227,7 +3266,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="57" t="s">
         <v>61</v>
       </c>
@@ -3242,7 +3281,7 @@
       <c r="E16" s="63">
         <v>21070.11</v>
       </c>
-      <c r="F16" s="219">
+      <c r="F16" s="187">
         <f>E16</f>
         <v>21070.11</v>
       </c>
@@ -3283,7 +3322,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="57" t="s">
         <v>62</v>
       </c>
@@ -3298,7 +3337,7 @@
       <c r="E17" s="63">
         <v>14590.12</v>
       </c>
-      <c r="F17" s="219"/>
+      <c r="F17" s="187"/>
       <c r="G17" s="64"/>
       <c r="H17" s="65">
         <f t="shared" si="0"/>
@@ -3336,7 +3375,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="57" t="s">
         <v>60</v>
       </c>
@@ -3351,7 +3390,7 @@
       <c r="E18" s="63">
         <v>41852.129999999997</v>
       </c>
-      <c r="F18" s="219">
+      <c r="F18" s="187">
         <f>49540-F21</f>
         <v>41851.839999999997</v>
       </c>
@@ -3390,13 +3429,13 @@
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="57"/>
       <c r="B19" s="57"/>
       <c r="C19" s="58"/>
       <c r="D19" s="62"/>
       <c r="E19" s="63"/>
-      <c r="F19" s="219"/>
+      <c r="F19" s="187"/>
       <c r="G19" s="64"/>
       <c r="H19" s="65"/>
       <c r="I19" s="65"/>
@@ -3411,7 +3450,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="57" t="s">
         <v>63</v>
       </c>
@@ -3426,7 +3465,7 @@
       <c r="E20" s="63">
         <v>7919.15</v>
       </c>
-      <c r="F20" s="219">
+      <c r="F20" s="187">
         <f>E20</f>
         <v>7919.15</v>
       </c>
@@ -3462,7 +3501,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="57" t="s">
         <v>64</v>
       </c>
@@ -3477,7 +3516,7 @@
       <c r="E21" s="63">
         <v>7688.16</v>
       </c>
-      <c r="F21" s="219">
+      <c r="F21" s="187">
         <f>E21</f>
         <v>7688.16</v>
       </c>
@@ -3516,7 +3555,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="57" t="s">
         <v>65</v>
       </c>
@@ -3531,7 +3570,7 @@
       <c r="E22" s="63">
         <v>7688.17</v>
       </c>
-      <c r="F22" s="219"/>
+      <c r="F22" s="187"/>
       <c r="G22" s="64"/>
       <c r="H22" s="65">
         <f t="shared" si="0"/>
@@ -3564,7 +3603,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="57" t="s">
         <v>66</v>
       </c>
@@ -3579,7 +3618,7 @@
       <c r="E23" s="63">
         <v>7910.18</v>
       </c>
-      <c r="F23" s="219">
+      <c r="F23" s="187">
         <f>E23</f>
         <v>7910.18</v>
       </c>
@@ -3615,7 +3654,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="57" t="s">
         <v>67</v>
       </c>
@@ -3630,7 +3669,7 @@
       <c r="E24" s="63">
         <v>7688.19</v>
       </c>
-      <c r="F24" s="219"/>
+      <c r="F24" s="187"/>
       <c r="G24" s="64"/>
       <c r="H24" s="65">
         <f t="shared" si="0"/>
@@ -3668,7 +3707,7 @@
         <v>0.19000000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="71"/>
       <c r="B25" s="72"/>
       <c r="C25" s="72"/>
@@ -3721,78 +3760,71 @@
         <v>3854848.7600000002</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
       <c r="D26" s="119"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B27" s="190" t="s">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B27" s="194" t="s">
         <v>85</v>
       </c>
-      <c r="C27" s="190"/>
-      <c r="D27" s="190"/>
-      <c r="E27" s="190"/>
-      <c r="F27" s="190"/>
-      <c r="G27" s="190"/>
-      <c r="H27" s="190"/>
-      <c r="I27" s="190"/>
-      <c r="J27" s="190"/>
-      <c r="K27" s="190"/>
-      <c r="L27" s="190"/>
-      <c r="M27" s="190"/>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B28" s="190"/>
-      <c r="C28" s="190"/>
-      <c r="D28" s="190"/>
-      <c r="E28" s="190"/>
-      <c r="F28" s="190"/>
-      <c r="G28" s="190"/>
-      <c r="H28" s="190"/>
-      <c r="I28" s="190"/>
-      <c r="J28" s="190"/>
-      <c r="K28" s="190"/>
-      <c r="L28" s="190"/>
-      <c r="M28" s="190"/>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B29" s="190"/>
-      <c r="C29" s="190"/>
-      <c r="D29" s="190"/>
-      <c r="E29" s="190"/>
-      <c r="F29" s="190"/>
-      <c r="G29" s="190"/>
-      <c r="H29" s="190"/>
-      <c r="I29" s="190"/>
-      <c r="J29" s="190"/>
-      <c r="K29" s="190"/>
-      <c r="L29" s="190"/>
-      <c r="M29" s="190"/>
-    </row>
-    <row r="30" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B30" s="190"/>
-      <c r="C30" s="190"/>
-      <c r="D30" s="190"/>
-      <c r="E30" s="190"/>
-      <c r="F30" s="190"/>
-      <c r="G30" s="190"/>
-      <c r="H30" s="190"/>
-      <c r="I30" s="190"/>
-      <c r="J30" s="190"/>
-      <c r="K30" s="190"/>
-      <c r="L30" s="190"/>
-      <c r="M30" s="190"/>
+      <c r="C27" s="194"/>
+      <c r="D27" s="194"/>
+      <c r="E27" s="194"/>
+      <c r="F27" s="194"/>
+      <c r="G27" s="194"/>
+      <c r="H27" s="194"/>
+      <c r="I27" s="194"/>
+      <c r="J27" s="194"/>
+      <c r="K27" s="194"/>
+      <c r="L27" s="194"/>
+      <c r="M27" s="194"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B28" s="194"/>
+      <c r="C28" s="194"/>
+      <c r="D28" s="194"/>
+      <c r="E28" s="194"/>
+      <c r="F28" s="194"/>
+      <c r="G28" s="194"/>
+      <c r="H28" s="194"/>
+      <c r="I28" s="194"/>
+      <c r="J28" s="194"/>
+      <c r="K28" s="194"/>
+      <c r="L28" s="194"/>
+      <c r="M28" s="194"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="B29" s="194"/>
+      <c r="C29" s="194"/>
+      <c r="D29" s="194"/>
+      <c r="E29" s="194"/>
+      <c r="F29" s="194"/>
+      <c r="G29" s="194"/>
+      <c r="H29" s="194"/>
+      <c r="I29" s="194"/>
+      <c r="J29" s="194"/>
+      <c r="K29" s="194"/>
+      <c r="L29" s="194"/>
+      <c r="M29" s="194"/>
+    </row>
+    <row r="30" spans="1:17" ht="72" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="194"/>
+      <c r="C30" s="194"/>
+      <c r="D30" s="194"/>
+      <c r="E30" s="194"/>
+      <c r="F30" s="194"/>
+      <c r="G30" s="194"/>
+      <c r="H30" s="194"/>
+      <c r="I30" s="194"/>
+      <c r="J30" s="194"/>
+      <c r="K30" s="194"/>
+      <c r="L30" s="194"/>
+      <c r="M30" s="194"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="H4:H5"/>
     <mergeCell ref="B2:H3"/>
     <mergeCell ref="O4:O5"/>
     <mergeCell ref="B27:M30"/>
@@ -3802,6 +3834,13 @@
     <mergeCell ref="J4:J5"/>
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="L4:L5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="H4:H5"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
@@ -3811,41 +3850,41 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{642D1833-D35F-45AC-9D7A-9C6C07C828FD}">
   <dimension ref="A1:Q32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" hidden="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" hidden="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5546875" customWidth="1"/>
-    <col min="4" max="4" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="7.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="212" t="s">
+    <row r="1" spans="1:17" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="216" t="s">
         <v>69</v>
       </c>
-      <c r="B1" s="213"/>
-      <c r="C1" s="213"/>
-      <c r="D1" s="213"/>
-      <c r="E1" s="213"/>
-      <c r="F1" s="213"/>
-      <c r="G1" s="213"/>
-      <c r="H1" s="213"/>
-      <c r="I1" s="213"/>
-      <c r="J1" s="213"/>
-      <c r="K1" s="213"/>
-      <c r="L1" s="213"/>
-      <c r="M1" s="214"/>
-    </row>
-    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="217"/>
+      <c r="C1" s="217"/>
+      <c r="D1" s="217"/>
+      <c r="E1" s="217"/>
+      <c r="F1" s="217"/>
+      <c r="G1" s="217"/>
+      <c r="H1" s="217"/>
+      <c r="I1" s="217"/>
+      <c r="J1" s="217"/>
+      <c r="K1" s="217"/>
+      <c r="L1" s="217"/>
+      <c r="M1" s="218"/>
+    </row>
+    <row r="2" spans="1:17" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="126"/>
       <c r="B2" s="126" t="s">
         <v>69</v>
@@ -3865,31 +3904,31 @@
       <c r="M2" s="121"/>
       <c r="N2" s="124"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="126"/>
       <c r="B3" s="125" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="217">
+      <c r="C3" s="221">
         <f>D2</f>
         <v>2521214.02</v>
       </c>
-      <c r="D3" s="217"/>
+      <c r="D3" s="221"/>
       <c r="E3" s="128"/>
       <c r="F3" s="128"/>
       <c r="G3" s="128"/>
       <c r="H3" s="129"/>
       <c r="I3" s="123"/>
       <c r="J3" s="130"/>
-      <c r="K3" s="215">
+      <c r="K3" s="219">
         <f>D2-I24</f>
         <v>858773.02</v>
       </c>
-      <c r="L3" s="215"/>
+      <c r="L3" s="219"/>
       <c r="M3" s="131"/>
       <c r="N3" s="124"/>
     </row>
-    <row r="4" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="132" t="s">
         <v>70</v>
       </c>
@@ -3931,7 +3970,7 @@
       </c>
       <c r="N4" s="124"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="139">
         <v>1</v>
       </c>
@@ -3981,7 +4020,7 @@
       </c>
       <c r="N5" s="124"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="149">
         <v>2</v>
       </c>
@@ -4031,7 +4070,7 @@
       </c>
       <c r="N6" s="124"/>
     </row>
-    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="139">
         <v>3</v>
       </c>
@@ -4084,7 +4123,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="139">
         <v>4</v>
       </c>
@@ -4134,7 +4173,7 @@
       </c>
       <c r="N8" s="124"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="139">
         <v>6</v>
       </c>
@@ -4184,7 +4223,7 @@
       </c>
       <c r="N9" s="124"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="139">
         <v>7</v>
       </c>
@@ -4233,7 +4272,7 @@
         <v>196313.01492019495</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="139">
         <v>8</v>
       </c>
@@ -4282,7 +4321,7 @@
         <v>79981.119880194965</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="139">
         <v>9</v>
       </c>
@@ -4331,7 +4370,7 @@
         <v>220779.15626019496</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="139">
         <v>10</v>
       </c>
@@ -4380,7 +4419,7 @@
         <v>110315.01492019495</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="139">
         <v>11</v>
       </c>
@@ -4429,7 +4468,7 @@
         <v>371481.11988019495</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="139">
         <v>12</v>
       </c>
@@ -4478,7 +4517,7 @@
         <v>113232.15626019496</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="139">
         <v>13</v>
       </c>
@@ -4527,7 +4566,7 @@
         <v>37781.014920194961</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="139">
         <v>14</v>
       </c>
@@ -4576,7 +4615,7 @@
         <v>647935.08350019495</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="139">
         <v>15</v>
       </c>
@@ -4595,7 +4634,7 @@
       <c r="L18" s="147"/>
       <c r="M18" s="145"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="139">
         <v>16</v>
       </c>
@@ -4644,7 +4683,7 @@
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="139">
         <v>17</v>
       </c>
@@ -4693,7 +4732,7 @@
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="139">
         <v>18</v>
       </c>
@@ -4742,7 +4781,7 @@
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="139">
         <v>19</v>
       </c>
@@ -4784,7 +4823,7 @@
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="139">
         <v>20</v>
       </c>
@@ -4823,7 +4862,7 @@
         <v>19131.554520194957</v>
       </c>
     </row>
-    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="139">
         <v>24</v>
       </c>
@@ -4853,7 +4892,7 @@
       </c>
       <c r="N24" s="39"/>
     </row>
-    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="123"/>
       <c r="C25" s="160"/>
       <c r="D25" s="161"/>
@@ -4873,39 +4912,39 @@
       <c r="L25" s="163"/>
       <c r="M25" s="163"/>
     </row>
-    <row r="26" spans="1:14" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:14" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="168" t="s">
         <v>80</v>
       </c>
-      <c r="C26" s="216"/>
-      <c r="D26" s="213"/>
-      <c r="E26" s="213"/>
-      <c r="F26" s="213"/>
-      <c r="G26" s="213"/>
-      <c r="H26" s="213"/>
-      <c r="I26" s="213"/>
-      <c r="J26" s="213"/>
-      <c r="K26" s="213"/>
-      <c r="L26" s="213"/>
-      <c r="M26" s="213"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C26" s="220"/>
+      <c r="D26" s="217"/>
+      <c r="E26" s="217"/>
+      <c r="F26" s="217"/>
+      <c r="G26" s="217"/>
+      <c r="H26" s="217"/>
+      <c r="I26" s="217"/>
+      <c r="J26" s="217"/>
+      <c r="K26" s="217"/>
+      <c r="L26" s="217"/>
+      <c r="M26" s="217"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H27" s="167"/>
       <c r="I27" s="169"/>
       <c r="J27" s="169"/>
       <c r="K27" s="169"/>
       <c r="M27" s="148"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E29" s="2"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="K30" s="170"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="K31" s="169"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E32" s="171"/>
       <c r="F32" s="171"/>
       <c r="G32" s="171"/>
@@ -4922,6 +4961,6 @@
     <mergeCell ref="C3:D3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="85" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>